--- a/outputs/marine_equipment/Сравнение_с_конкурентом.xlsx
+++ b/outputs/marine_equipment/Сравнение_с_конкурентом.xlsx
@@ -979,7 +979,7 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>— Сравнение по типу и диаметру приблизительное: в одной строке у конкурента может стоять бронза, а у нас сталь. Решения по ценам принимаем по совпадениям по чертежу.</t>
+          <t>— Вся наша арматура бронзовая или латунная, включая все клинкеты. Стальными идут только паровой и редукционные клапаны. Поэтому сравниваем с бронзовой колонкой конкурента: его стальные позиции втрое дешевле и к нам отношения не имеют.</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Бронза и сталь показаны отдельно: у конкурента разница между ними втрое. Материал наших позиций в учете чаще не указан, поэтому сравнивать надо с тем столбцом, который соответствует факту на складе.</t>
+          <t>Вся наша арматура бронзовая или латунная, поэтому сравниваем с бронзовой колонкой конкурента. Стальная приведена справочно: у него она втрое дешевле, и путать их нельзя.</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,11 @@
       <c r="K39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>у конкурента только сталь, сравнивать не с чем</t>
+        </is>
+      </c>
       <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
@@ -4071,7 +4075,11 @@
       <c r="K43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>у конкурента только сталь, сравнивать не с чем</t>
+        </is>
+      </c>
       <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
